--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>SpectraA Technology Solutions NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹27 (22.88%) 27 ↓ / 27 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹42.52 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>22-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>24-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>13-Sep 18:57</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Maharaja &amp; Speedex India BSE SMEO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹48 (25.81%) 15 ↓ / 48 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹50 (26.88%) 15 ↓ / 50 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.48x</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹80.13 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>10-Sep GMP: 30</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>16-Sep</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>18-Sep</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>13-Sep 13:30</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>13-Sep 18:56</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹27 (22.88%) 27 ↓ / 27 ↑</t>
+          <t>₹40 (33.90%) 27 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 13:57</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹50 (26.88%) 15 ↓ / 50 ↑</t>
+          <t>₹45 (24.19%) 15 ↓ / 48 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Sep 18:56</t>
+          <t>14-Sep 14:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEU</t>
+          <t>Robokidz Eduventures BSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹40 (33.90%) 27 ↓ / 40 ↑</t>
+          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹42.52 Cr</t>
+          <t>₹31.09 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -521,27 +521,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>21-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>23-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>22-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Sep 13:57</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,65 +553,199 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SpectraA Technology Solutions NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹44 (37.29%) 27 ↓ / 44 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹42.52 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>22-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>24-Sep</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>14-Sep 20:54</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Maharaja &amp; Speedex India BSE SMEO</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹45 (24.19%) 15 ↓ / 48 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹40 (21.51%) 15 ↓ / 48 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.48x</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹80.13 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>600</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>10-Sep GMP: 30</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>15-Sep</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>16-Sep</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>18-Sep</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>14-Sep 14:01</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>14-Sep 21:01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Raksan Transformers BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹58 (21.25%) 25 ↓ / 58 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.31x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>₹150.50 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>10-Sep GMP: 28</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15-Sep</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>16-Sep</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>14-Sep 20:53</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>SpectraA Technology Solutions NSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
+          <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹31.09 Cr</t>
+          <t>₹42.52 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -521,231 +521,30 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>21-Sep</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>23-Sep</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>22-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>24-Sep</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SpectraA Technology Solutions NSE SMEU</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹44 (37.29%) 27 ↓ / 44 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹42.52 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>21-Sep</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>22-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>24-Sep</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>14-Sep 20:54</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Maharaja &amp; Speedex India BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹40 (21.51%) 15 ↓ / 48 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.48x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹80.13 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 30</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>18-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>14-Sep 21:01</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Raksan Transformers BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹58 (21.25%) 25 ↓ / 58 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.31x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹150.50 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>10-Sep GMP: 28</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15-Sep</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>18-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>14-Sep 20:53</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:33</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,67 +486,201 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Robokidz Eduventures BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹31.09 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>21-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>24-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>16-Sep 12:53</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>SpectraA Technology Solutions NSE SMEU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>118</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹42.52 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>17-Sep</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>21-Sep</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>22-Sep</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>24-Sep</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>15-Sep 19:33</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>16-Sep 12:56</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Vama Wovenfab BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹70 (20.53%) 10 ↓ / 70 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.07x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹49.54 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>15-Sep GMP: 30</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>17-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>18-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>22-Sep</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>16-Sep 13:01</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 18:58</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Sep 12:56</t>
+          <t>16-Sep 18:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.07x</t>
+          <t>0.45x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>16-Sep 13:01</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹45 (42.45%) 45 ↓ / 45 ↑</t>
+          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Sep 18:58</t>
+          <t>17-Sep 13:56</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEU</t>
+          <t>SpectraA Technology Solutions NSE SMEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹50 (42.37%) 27 ↓ / 50 ↑</t>
+          <t>₹30 (25.42%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.77x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17-Sep</t>
+          <t>17-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,79 +608,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Sep 18:56</t>
+          <t>17-Sep 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vama Wovenfab BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹70 (20.53%) 10 ↓ / 70 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.45x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹49.54 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>15-Sep GMP: 30</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>18-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>22-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>16-Sep 18:54</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>❌</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Sep 13:56</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.77x</t>
+          <t>5.66x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Sep 14:02</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.66x</t>
+          <t>14.36x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹30 (25.42%) 27 ↓ / 50 ↑</t>
+          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.36x</t>
+          <t>19.9x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Sep 13:37</t>
+          <t>18-Sep 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.9x</t>
+          <t>19.93x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Sep 18:37</t>
+          <t>19-Sep 13:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,22 +486,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEU</t>
+          <t>Robokidz Eduventures BSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹51 (48.11%) 45 ↓ / 51 ↑</t>
+          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.05x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>21-Sep GMP: 55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SpectraA Technology Solutions NSE SMEO</t>
+          <t>SpectraA Technology Solutions NSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.93x</t>
+          <t>152.54x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>21-Sep</t>
+          <t>21-Sep GMP: 45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.05x</t>
+          <t>9.29x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,77 +541,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SpectraA Technology Solutions NSE SMECT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹45 (38.14%) 27 ↓ / 50 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>152.54x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹42.52 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>17-Sep GMP: 30</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>21-Sep GMP: 45</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>22-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>24-Sep</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>21-Sep 14:02</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Roopa Screen BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹14 (21.88%) 14 ↓ / 14 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹19.20 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>22-Sep 13:37</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Robokidz Eduventures BSE SMEO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9.29x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>43.18x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹31.09 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>21-Sep GMP: 55</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>23-Sep</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>24-Sep</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>28-Sep</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>21-Sep 21:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>22-Sep 13:37</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹55 (51.89%) 45 ↓ / 55 ↑</t>
+          <t>₹65 (61.32%) 45 ↓ / 65 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.18x</t>
+          <t>72.74x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Robokidz Eduventures BSE SMEO</t>
+          <t>Robokidz Eduventures BSE SMECT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>72.74x</t>
+          <t>471.12x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 65</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,140 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Roopa Screen BSE SMEU</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹14 (21.88%) 14 ↓ / 14 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹19.20 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>24-Sep</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>23-Sep 13:37</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Robokidz Eduventures BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹65 (61.32%) 45 ↓ / 65 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>471.12x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹31.09 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>21-Sep GMP: 55</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23-Sep GMP: 65</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>24-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>23-Sep 13:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Roopa Screen BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹29 (45.31%) 8 ↓ / 29 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.12x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹19.20 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24-Sep GMP: 29</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24-Sep 16:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Roopa Screen BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹29 (45.31%) 8 ↓ / 29 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1.12x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹19.20 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>24-Sep GMP: 29</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>24-Sep 16:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,140 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vans Electroengineerings BSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹28 (23.73%) 28 ↓ / 28 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹33.98 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>7-Oct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>26-Sep 19:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Roopa Screen BSE SMEO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹32 (50.00%) 8 ↓ / 32 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.35x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹19.20 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>24-Sep GMP: 0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>26-Sep 19:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹28 (23.73%) 28 ↓ / 28 ↑</t>
+          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
+          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -526,22 +526,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,65 +553,132 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMEO</t>
+          <t>Vans Electroengineerings BSE SMEU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹32 (50.00%) 8 ↓ / 32 ↑</t>
+          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹33.98 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>7-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>28-Sep 15:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Roopa Screen BSE SMECT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹38 (59.38%) 8 ↓ / 38 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5.35x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>206.23x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹19.20 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>2000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>24-Sep GMP: 0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>28-Sep GMP: 38</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>29-Sep</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>1-Oct</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>27-Sep 19:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>28-Sep 15:02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEU</t>
+          <t>EverestIMS Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
+          <t>₹17 (20.00%) 13 ↓ / 17 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.11x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMEU</t>
+          <t>Vans Electroengineerings BSE SMEO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.84x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>29-Sep GMP: 45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,32 +620,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Roopa Screen BSE SMECT</t>
+          <t>Shivchem Agro BSE SMEO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹38 (59.38%) 8 ↓ / 38 ↑</t>
+          <t>₹13 (20.97%) 6 ↓ / 13 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>206.23x</t>
+          <t>0.5x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹19.20 Cr</t>
+          <t>₹14.01 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -655,30 +655,97 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 0</t>
+          <t>28-Sep GMP: 6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 38</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bench Mark Infotech Services NSE SMECT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>₹30 (27.27%) 12 ↓ / 30 ↑</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>69.36x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>₹42.44 Cr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>25-Sep GMP: 16</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>29-Sep GMP: 30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>29-Sep 15:02</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹17 (20.00%) 13 ↓ / 17 ↑</t>
+          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.11x</t>
+          <t>0.36x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 17</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,17 +558,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹45 (38.14%) 45 ↓ / 45 ↑</t>
+          <t>₹90 (76.27%) 45 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.84x</t>
+          <t>42.1x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 45</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,144 +608,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Shivchem Agro BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹13 (20.97%) 6 ↓ / 13 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.5x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹14.01 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>28-Sep GMP: 6</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>29-Sep 15:02</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>❌</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Bench Mark Infotech Services NSE SMECT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹30 (27.27%) 12 ↓ / 30 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>69.36x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹42.44 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>25-Sep GMP: 16</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>29-Sep GMP: 30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>29-Sep 15:02</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,132 +486,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEO</t>
+          <t>Vans Electroengineerings BSE SMECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹20 (23.53%) 13 ↓ / 20 ↑</t>
+          <t>₹70 (59.32%) 45 ↓ / 90 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.36x</t>
+          <t>596.79x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹33.98 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>29-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>1-Oct GMP: 70</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>5-Oct</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>30-Sep 14:37</t>
+          <t>1-Oct 15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Vans Electroengineerings BSE SMEO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹90 (76.27%) 45 ↓ / 90 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>42.1x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹33.98 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>29-Sep GMP: 90</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>30-Sep 14:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,62 +486,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vans Electroengineerings BSE SMECT</t>
+          <t>EverestIMS Technologies BSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹70 (59.32%) 45 ↓ / 90 ↑</t>
+          <t>₹28 (32.94%) 13 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>596.79x</t>
+          <t>1.7x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>85</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹33.98 Cr</t>
+          <t>₹48.46 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 90</t>
+          <t>29-Sep GMP: 16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1-Oct GMP: 70</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>7-Oct</t>
+          <t>8-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-Oct 15:37</t>
+          <t>2-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹28 (32.94%) 13 ↓ / 28 ↑</t>
+          <t>₹40 (47.06%) 13 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-Oct 15:02</t>
+          <t>3-Oct 14:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Oct 14:37</t>
+          <t>3-Oct 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-Oct 19:37</t>
+          <t>4-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMEO</t>
+          <t>EverestIMS Technologies BSE SMECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹40 (47.06%) 13 ↓ / 40 ↑</t>
+          <t>₹42 (49.41%) 13 ↓ / 42 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.7x</t>
+          <t>279.29x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>5-Oct GMP: 42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-Oct 15:02</t>
+          <t>5-Oct 15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EverestIMS Technologies BSE SMECT</t>
+          <t>Acme India Industries BSE SMECT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹42 (49.41%) 13 ↓ / 42 ↑</t>
+          <t>₹50 (25.51%) 25 ↓ / 50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,47 +501,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>279.29x</t>
+          <t>117.34x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹48.46 Cr</t>
+          <t>₹121.69 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>600</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 16</t>
+          <t>30-Sep GMP: 30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5-Oct GMP: 42</t>
+          <t>6-Oct GMP: 50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>7-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8-Oct</t>
+          <t>9-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-Oct 15:37</t>
+          <t>6-Oct 15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Acme India Industries BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹50 (25.51%) 25 ↓ / 50 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>117.34x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹121.69 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>30-Sep GMP: 30</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6-Oct GMP: 50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>7-Oct</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>9-Oct</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>6-Oct 15:37</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rating▲▼</t>
+          <t>🔥Rating▲▼</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shellz India BSE SMECT</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹46 (25.70%) 25 ↓ / 46 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>17.76x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹59.97 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>19-Oct GMP: 46</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19-Oct 14:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Shellz India BSE SMECT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹46 (25.70%) 25 ↓ / 46 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>17.76x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹59.97 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>15-Oct</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>19-Oct GMP: 46</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>21-Oct</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>23-Oct</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>19-Oct 14:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Maxwell Engineering Solutions NSE SMEU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹52 (32.91%) 27 ↓ / 52 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹57.64 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30-Oct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3-Nov</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4-Nov</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6-Nov</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>29-Oct 15:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maxwell Engineering Solutions NSE SMEU</t>
+          <t>Maxwell Engineering Solutions NSE SMEO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹52 (32.91%) 27 ↓ / 52 ↑</t>
+          <t>₹70 (44.30%) 27 ↓ / 70 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.47x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-Oct</t>
+          <t>30-Oct GMP: 70</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Oct 15:02</t>
+          <t>30-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/SME_IPOs.xlsx
+++ b/files/SME_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>HGS (India) NSE SMEO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹30 (25.00%) 30 ↓ / 30 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.16x</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹34.56 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>30-Oct GMP: 30</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3-Nov</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4-Nov</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>6-Nov</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>31-Oct 15:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Maxwell Engineering Solutions NSE SMEO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>₹70 (44.30%) 27 ↓ / 70 ↑</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3.47x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.67x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹57.64 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>800</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>30-Oct GMP: 70</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>3-Nov</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>4-Nov</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>6-Nov</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>30-Oct 15:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>31-Oct 15:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
